--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -1834,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119532143</v>
+        <v>119532189</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>91825</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,25 +1846,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>1968</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555222</v>
+        <v>555432</v>
       </c>
       <c r="R13" t="n">
-        <v>6955368</v>
+        <v>6955262</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119532189</v>
+        <v>119532143</v>
       </c>
       <c r="B14" t="n">
-        <v>91825</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,25 +1948,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555432</v>
+        <v>555222</v>
       </c>
       <c r="R14" t="n">
-        <v>6955262</v>
+        <v>6955368</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119532173</v>
+        <v>119532214</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,25 +2157,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555080</v>
+        <v>555215</v>
       </c>
       <c r="R16" t="n">
-        <v>6955298</v>
+        <v>6955365</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119532214</v>
+        <v>119532173</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2259,25 +2259,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555215</v>
+        <v>555080</v>
       </c>
       <c r="R17" t="n">
-        <v>6955365</v>
+        <v>6955298</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119532211</v>
+        <v>119532135</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,38 +1010,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555292</v>
+        <v>555578</v>
       </c>
       <c r="R5" t="n">
-        <v>6955404</v>
+        <v>6955449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119532135</v>
+        <v>119532211</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,58 +1132,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555578</v>
+        <v>555292</v>
       </c>
       <c r="R6" t="n">
-        <v>6955449</v>
+        <v>6955404</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119532214</v>
+        <v>119532173</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,25 +2157,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555215</v>
+        <v>555080</v>
       </c>
       <c r="R16" t="n">
-        <v>6955365</v>
+        <v>6955298</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119532173</v>
+        <v>119532214</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2259,25 +2259,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555080</v>
+        <v>555215</v>
       </c>
       <c r="R17" t="n">
-        <v>6955298</v>
+        <v>6955365</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119532177</v>
+        <v>119532134</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555268</v>
+        <v>555449</v>
       </c>
       <c r="R3" t="n">
-        <v>6955365</v>
+        <v>6955393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +870,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119532152</v>
+        <v>119532189</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>91825</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +913,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555363</v>
+        <v>555432</v>
       </c>
       <c r="R4" t="n">
-        <v>6955341</v>
+        <v>6955262</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119532135</v>
+        <v>119532182</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,58 +1015,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555578</v>
+        <v>555396</v>
       </c>
       <c r="R5" t="n">
-        <v>6955449</v>
+        <v>6955386</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119532211</v>
+        <v>119532146</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1117,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555292</v>
+        <v>555445</v>
       </c>
       <c r="R6" t="n">
-        <v>6955404</v>
+        <v>6955336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,12 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,7 +1207,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119532179</v>
+        <v>119532152</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1262,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555273</v>
+        <v>555363</v>
       </c>
       <c r="R7" t="n">
-        <v>6955369</v>
+        <v>6955341</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,12 +1277,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119532200</v>
+        <v>119532171</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,25 +1321,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1364,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555451</v>
+        <v>555162</v>
       </c>
       <c r="R8" t="n">
-        <v>6955405</v>
+        <v>6955287</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119532175</v>
+        <v>119532209</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,25 +1423,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555175</v>
+        <v>555183</v>
       </c>
       <c r="R9" t="n">
-        <v>6955324</v>
+        <v>6955343</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1513,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119532146</v>
+        <v>119532150</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1568,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555445</v>
+        <v>555381</v>
       </c>
       <c r="R10" t="n">
-        <v>6955336</v>
+        <v>6955359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1615,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119532202</v>
+        <v>119532200</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1670,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555532</v>
+        <v>555451</v>
       </c>
       <c r="R11" t="n">
-        <v>6955432</v>
+        <v>6955405</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119532198</v>
+        <v>119532142</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,34 +1733,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555391</v>
+        <v>555408</v>
       </c>
       <c r="R12" t="n">
-        <v>6955385</v>
+        <v>6955266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,12 +1791,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>hörd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1834,10 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119532189</v>
+        <v>119532120</v>
       </c>
       <c r="B13" t="n">
-        <v>91825</v>
+        <v>87406</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1850,21 +1844,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555432</v>
+        <v>555364</v>
       </c>
       <c r="R13" t="n">
-        <v>6955262</v>
+        <v>6955302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,10 +1930,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119532143</v>
+        <v>119532175</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,25 +1942,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1976,10 +1970,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555222</v>
+        <v>555175</v>
       </c>
       <c r="R14" t="n">
-        <v>6955368</v>
+        <v>6955324</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,10 +2032,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119532133</v>
+        <v>119532141</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>91843</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2050,25 +2044,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6003297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spricktaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum glaucopus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2078,10 +2072,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555107</v>
+        <v>555221</v>
       </c>
       <c r="R15" t="n">
-        <v>6955310</v>
+        <v>6955359</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,17 +2110,13 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2145,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119532173</v>
+        <v>119532206</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,25 +2147,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555080</v>
+        <v>555084</v>
       </c>
       <c r="R16" t="n">
-        <v>6955298</v>
+        <v>6955311</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119532214</v>
+        <v>119532202</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,21 +2253,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555215</v>
+        <v>555532</v>
       </c>
       <c r="R17" t="n">
-        <v>6955365</v>
+        <v>6955432</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,10 +2339,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119532209</v>
+        <v>119532177</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2361,25 +2351,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2389,10 +2379,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555183</v>
+        <v>555268</v>
       </c>
       <c r="R18" t="n">
-        <v>6955343</v>
+        <v>6955365</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,10 +2441,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119532182</v>
+        <v>119532140</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>100080</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2463,25 +2453,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2481,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555396</v>
+        <v>555631</v>
       </c>
       <c r="R19" t="n">
-        <v>6955386</v>
+        <v>6955317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,10 +2543,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119532171</v>
+        <v>119532198</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2565,25 +2555,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,10 +2583,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555162</v>
+        <v>555391</v>
       </c>
       <c r="R20" t="n">
-        <v>6955287</v>
+        <v>6955385</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,7 +2645,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119532150</v>
+        <v>119532179</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2695,10 +2685,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555381</v>
+        <v>555273</v>
       </c>
       <c r="R21" t="n">
-        <v>6955359</v>
+        <v>6955369</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,12 +2715,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2757,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119532187</v>
+        <v>119532211</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2769,25 +2759,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2797,10 +2787,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555182</v>
+        <v>555292</v>
       </c>
       <c r="R22" t="n">
-        <v>6955285</v>
+        <v>6955404</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2859,10 +2849,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119532142</v>
+        <v>119532187</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,38 +2865,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555408</v>
+        <v>555182</v>
       </c>
       <c r="R23" t="n">
-        <v>6955266</v>
+        <v>6955285</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2933,17 +2919,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>hörd</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2970,7 +2951,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119532134</v>
+        <v>119532135</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3003,17 +2984,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555449</v>
+        <v>555578</v>
       </c>
       <c r="R24" t="n">
-        <v>6955393</v>
+        <v>6955449</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,11 +3047,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3077,10 +3073,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119532148</v>
+        <v>119532143</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>91852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3089,25 +3085,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3117,10 +3113,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555393</v>
+        <v>555222</v>
       </c>
       <c r="R25" t="n">
-        <v>6955361</v>
+        <v>6955368</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3147,12 +3143,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,10 +3175,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119532120</v>
+        <v>119532173</v>
       </c>
       <c r="B26" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3191,25 +3187,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3219,10 +3215,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555364</v>
+        <v>555080</v>
       </c>
       <c r="R26" t="n">
-        <v>6955302</v>
+        <v>6955298</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,12 +3245,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3281,10 +3277,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119532206</v>
+        <v>119532133</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3293,25 +3289,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3317,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555084</v>
+        <v>555107</v>
       </c>
       <c r="R27" t="n">
-        <v>6955311</v>
+        <v>6955310</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,6 +3353,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3383,10 +3384,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119532141</v>
+        <v>119532214</v>
       </c>
       <c r="B28" t="n">
-        <v>91843</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3395,25 +3396,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003297</v>
+        <v>4368</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3423,10 +3424,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555221</v>
+        <v>555215</v>
       </c>
       <c r="R28" t="n">
-        <v>6955359</v>
+        <v>6955365</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,7 +3468,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119532140</v>
+        <v>119532148</v>
       </c>
       <c r="B29" t="n">
-        <v>100080</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3498,25 +3498,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555631</v>
+        <v>555393</v>
       </c>
       <c r="R29" t="n">
-        <v>6955317</v>
+        <v>6955361</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119532146</v>
+        <v>119532209</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,25 +1117,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555445</v>
+        <v>555183</v>
       </c>
       <c r="R6" t="n">
-        <v>6955336</v>
+        <v>6955343</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,7 +1207,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119532152</v>
+        <v>119532146</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555363</v>
+        <v>555445</v>
       </c>
       <c r="R7" t="n">
-        <v>6955341</v>
+        <v>6955336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119532171</v>
+        <v>119532152</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555162</v>
+        <v>555363</v>
       </c>
       <c r="R8" t="n">
-        <v>6955287</v>
+        <v>6955341</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119532209</v>
+        <v>119532171</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,25 +1423,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555183</v>
+        <v>555162</v>
       </c>
       <c r="R9" t="n">
-        <v>6955343</v>
+        <v>6955287</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119532141</v>
+        <v>119532206</v>
       </c>
       <c r="B15" t="n">
-        <v>91843</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2044,25 +2044,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003297</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555221</v>
+        <v>555084</v>
       </c>
       <c r="R15" t="n">
-        <v>6955359</v>
+        <v>6955311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,7 +2116,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2135,10 +2134,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119532206</v>
+        <v>119532141</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91843</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,25 +2146,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6003297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spricktaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum glaucopus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2174,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555084</v>
+        <v>555221</v>
       </c>
       <c r="R16" t="n">
-        <v>6955311</v>
+        <v>6955359</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,6 +2218,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119532198</v>
+        <v>119532179</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,25 +2555,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555391</v>
+        <v>555273</v>
       </c>
       <c r="R20" t="n">
-        <v>6955385</v>
+        <v>6955369</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119532179</v>
+        <v>119532198</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,25 +2657,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555273</v>
+        <v>555391</v>
       </c>
       <c r="R21" t="n">
-        <v>6955369</v>
+        <v>6955385</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3586,6 +3586,843 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124766514</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>555385</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6955319</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124765997</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>555481</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6955375</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124766516</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>555312</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6955333</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124766527</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>555322</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6955344</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124766526</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>555434</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6955374</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124766529</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>555486</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6955384</v>
+      </c>
+      <c r="S35" t="n">
+        <v>50</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124765999</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>555621</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6955246</v>
+      </c>
+      <c r="S36" t="n">
+        <v>50</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124766514</v>
+        <v>124766526</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3604,16 +3604,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3621,10 +3621,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3633,13 +3637,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555385</v>
+        <v>555434</v>
       </c>
       <c r="R30" t="n">
-        <v>6955319</v>
+        <v>6955374</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3666,14 +3670,19 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>barkfläk färsk tall</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3700,7 +3709,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124765997</v>
+        <v>124766527</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3733,28 +3742,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555481</v>
+        <v>555322</v>
       </c>
       <c r="R31" t="n">
-        <v>6955375</v>
+        <v>6955344</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3783,7 +3793,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3793,7 +3803,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3942,7 +3952,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124766527</v>
+        <v>124765997</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3975,29 +3985,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555322</v>
+        <v>555481</v>
       </c>
       <c r="R33" t="n">
-        <v>6955344</v>
+        <v>6955375</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4026,7 +4035,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4036,7 +4045,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4063,10 +4072,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124766526</v>
+        <v>124765999</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4075,20 +4084,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4096,26 +4105,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555434</v>
+        <v>555621</v>
       </c>
       <c r="R34" t="n">
-        <v>6955374</v>
+        <v>6955246</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4147,7 +4155,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4157,7 +4165,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4184,10 +4192,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766529</v>
+        <v>124766514</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4200,16 +4208,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4217,14 +4225,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4233,13 +4237,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555486</v>
+        <v>555385</v>
       </c>
       <c r="R35" t="n">
-        <v>6955384</v>
+        <v>6955319</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4266,19 +4270,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>06:38</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>06:38</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4305,10 +4304,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124765999</v>
+        <v>124766529</v>
       </c>
       <c r="B36" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4317,20 +4316,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4338,25 +4337,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555621</v>
+        <v>555486</v>
       </c>
       <c r="R36" t="n">
-        <v>6955246</v>
+        <v>6955384</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124766526</v>
+        <v>124766514</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3604,16 +3604,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3621,14 +3621,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3637,13 +3633,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555434</v>
+        <v>555385</v>
       </c>
       <c r="R30" t="n">
-        <v>6955374</v>
+        <v>6955319</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3670,19 +3666,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>06:40</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3709,7 +3700,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124766527</v>
+        <v>124765997</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3742,29 +3733,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555322</v>
+        <v>555481</v>
       </c>
       <c r="R31" t="n">
-        <v>6955344</v>
+        <v>6955375</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3793,7 +3783,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3803,7 +3793,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3952,7 +3942,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124765997</v>
+        <v>124766527</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3985,28 +3975,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555481</v>
+        <v>555322</v>
       </c>
       <c r="R33" t="n">
-        <v>6955375</v>
+        <v>6955344</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4035,7 +4026,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4045,7 +4036,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4192,10 +4183,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766514</v>
+        <v>124766529</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4208,16 +4199,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4225,10 +4216,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4237,13 +4232,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555385</v>
+        <v>555486</v>
       </c>
       <c r="R35" t="n">
-        <v>6955319</v>
+        <v>6955384</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4270,14 +4265,19 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>barkfläk färsk tall</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766529</v>
+        <v>124766526</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555486</v>
+        <v>555434</v>
       </c>
       <c r="R36" t="n">
-        <v>6955384</v>
+        <v>6955374</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124766514</v>
+        <v>124766526</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3604,16 +3604,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3621,10 +3621,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3633,13 +3637,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555385</v>
+        <v>555434</v>
       </c>
       <c r="R30" t="n">
-        <v>6955319</v>
+        <v>6955374</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3666,14 +3670,19 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>barkfläk färsk tall</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3942,10 +3951,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124766527</v>
+        <v>124765999</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3954,20 +3963,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3975,26 +3984,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555322</v>
+        <v>555621</v>
       </c>
       <c r="R33" t="n">
-        <v>6955344</v>
+        <v>6955246</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4026,7 +4034,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4036,7 +4044,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4063,10 +4071,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124765999</v>
+        <v>124766527</v>
       </c>
       <c r="B34" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4075,20 +4083,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4096,25 +4104,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555621</v>
+        <v>555322</v>
       </c>
       <c r="R34" t="n">
-        <v>6955246</v>
+        <v>6955344</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4146,7 +4155,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4156,7 +4165,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4183,10 +4192,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766529</v>
+        <v>124766514</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4199,16 +4208,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4216,14 +4225,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4232,13 +4237,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555486</v>
+        <v>555385</v>
       </c>
       <c r="R35" t="n">
-        <v>6955384</v>
+        <v>6955319</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4265,19 +4270,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>06:38</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>06:38</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766526</v>
+        <v>124766529</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555434</v>
+        <v>555486</v>
       </c>
       <c r="R36" t="n">
-        <v>6955374</v>
+        <v>6955384</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,14 +3588,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124766526</v>
+        <v>124765997</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3621,29 +3621,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555434</v>
+        <v>555481</v>
       </c>
       <c r="R30" t="n">
-        <v>6955374</v>
+        <v>6955375</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3672,7 +3671,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3682,7 +3681,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3709,10 +3708,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124765997</v>
+        <v>124765999</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3721,20 +3720,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3747,7 +3746,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3757,13 +3756,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555481</v>
+        <v>555621</v>
       </c>
       <c r="R31" t="n">
-        <v>6955375</v>
+        <v>6955246</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3792,7 +3791,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3802,7 +3801,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3951,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124765999</v>
+        <v>124766514</v>
       </c>
       <c r="B33" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3963,20 +3962,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3985,27 +3984,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555621</v>
+        <v>555385</v>
       </c>
       <c r="R33" t="n">
-        <v>6955246</v>
+        <v>6955319</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4032,19 +4028,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>06:00</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4071,7 +4062,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124766527</v>
+        <v>124766529</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4120,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555322</v>
+        <v>555486</v>
       </c>
       <c r="R34" t="n">
-        <v>6955344</v>
+        <v>6955384</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4155,7 +4146,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4165,7 +4156,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4192,14 +4183,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766514</v>
+        <v>124766526</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4208,16 +4199,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4225,10 +4216,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4237,13 +4232,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555385</v>
+        <v>555434</v>
       </c>
       <c r="R35" t="n">
-        <v>6955319</v>
+        <v>6955374</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4270,14 +4265,19 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>barkfläk färsk tall</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766529</v>
+        <v>124766527</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555486</v>
+        <v>555322</v>
       </c>
       <c r="R36" t="n">
-        <v>6955384</v>
+        <v>6955344</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3708,10 +3708,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124765999</v>
+        <v>124766514</v>
       </c>
       <c r="B31" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3720,20 +3720,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3742,27 +3742,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555621</v>
+        <v>555385</v>
       </c>
       <c r="R31" t="n">
-        <v>6955246</v>
+        <v>6955319</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3789,19 +3786,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>06:00</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124766514</v>
+        <v>124765999</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3962,20 +3954,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3984,24 +3976,27 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555385</v>
+        <v>555621</v>
       </c>
       <c r="R33" t="n">
-        <v>6955319</v>
+        <v>6955246</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4028,14 +4023,19 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>barkfläk färsk tall</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,7 +4062,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124766529</v>
+        <v>124766527</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555486</v>
+        <v>555322</v>
       </c>
       <c r="R34" t="n">
-        <v>6955384</v>
+        <v>6955344</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766527</v>
+        <v>124766529</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555322</v>
+        <v>555486</v>
       </c>
       <c r="R36" t="n">
-        <v>6955344</v>
+        <v>6955384</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124765997</v>
+        <v>124765999</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3600,20 +3600,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555481</v>
+        <v>555621</v>
       </c>
       <c r="R30" t="n">
-        <v>6955375</v>
+        <v>6955246</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3708,10 +3708,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124766514</v>
+        <v>124765997</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3724,16 +3724,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3742,21 +3742,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555385</v>
+        <v>555481</v>
       </c>
       <c r="R31" t="n">
-        <v>6955319</v>
+        <v>6955375</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3786,14 +3789,19 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>barkfläk färsk tall</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3942,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124765999</v>
+        <v>124766514</v>
       </c>
       <c r="B33" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3954,20 +3962,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3976,27 +3984,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555621</v>
+        <v>555385</v>
       </c>
       <c r="R33" t="n">
-        <v>6955246</v>
+        <v>6955319</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4023,19 +4028,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>06:00</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4183,7 +4183,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766526</v>
+        <v>124766529</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555434</v>
+        <v>555486</v>
       </c>
       <c r="R35" t="n">
-        <v>6955374</v>
+        <v>6955384</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766529</v>
+        <v>124766526</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555486</v>
+        <v>555434</v>
       </c>
       <c r="R36" t="n">
-        <v>6955384</v>
+        <v>6955374</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124765999</v>
+        <v>124765997</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3600,20 +3600,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555621</v>
+        <v>555481</v>
       </c>
       <c r="R30" t="n">
-        <v>6955246</v>
+        <v>6955375</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3708,10 +3708,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124765997</v>
+        <v>124766514</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3724,16 +3724,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3742,24 +3742,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555481</v>
+        <v>555385</v>
       </c>
       <c r="R31" t="n">
-        <v>6955375</v>
+        <v>6955319</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3789,19 +3786,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>06:10</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3828,10 +3820,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124766516</v>
+        <v>124765999</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3840,20 +3832,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3862,24 +3854,27 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555312</v>
+        <v>555621</v>
       </c>
       <c r="R32" t="n">
-        <v>6955333</v>
+        <v>6955246</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3908,7 +3903,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3918,12 +3913,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3950,10 +3940,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124766514</v>
+        <v>124766516</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3966,16 +3956,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3995,10 +3985,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555385</v>
+        <v>555312</v>
       </c>
       <c r="R33" t="n">
-        <v>6955319</v>
+        <v>6955333</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4028,14 +4018,24 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>barkfläk färsk tall</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4183,7 +4183,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766529</v>
+        <v>124766526</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555486</v>
+        <v>555434</v>
       </c>
       <c r="R35" t="n">
-        <v>6955384</v>
+        <v>6955374</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766526</v>
+        <v>124766529</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555434</v>
+        <v>555486</v>
       </c>
       <c r="R36" t="n">
-        <v>6955374</v>
+        <v>6955384</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,7 +3588,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124765997</v>
+        <v>124766516</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3622,24 +3622,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555481</v>
+        <v>555312</v>
       </c>
       <c r="R30" t="n">
-        <v>6955375</v>
+        <v>6955333</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3671,7 +3668,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3681,7 +3678,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3940,7 +3942,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124766516</v>
+        <v>124765997</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3974,21 +3976,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555312</v>
+        <v>555481</v>
       </c>
       <c r="R33" t="n">
-        <v>6955333</v>
+        <v>6955375</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4020,7 +4025,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4030,12 +4035,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,7 +4062,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124766527</v>
+        <v>124766526</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555322</v>
+        <v>555434</v>
       </c>
       <c r="R34" t="n">
-        <v>6955344</v>
+        <v>6955374</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766526</v>
+        <v>124766529</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555434</v>
+        <v>555486</v>
       </c>
       <c r="R35" t="n">
-        <v>6955374</v>
+        <v>6955384</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766529</v>
+        <v>124766527</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555486</v>
+        <v>555322</v>
       </c>
       <c r="R36" t="n">
-        <v>6955384</v>
+        <v>6955344</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124766516</v>
+        <v>124765999</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3600,20 +3600,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3622,24 +3622,27 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555312</v>
+        <v>555621</v>
       </c>
       <c r="R30" t="n">
-        <v>6955333</v>
+        <v>6955246</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3668,7 +3671,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3678,12 +3681,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3822,10 +3820,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124765999</v>
+        <v>124765997</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3834,20 +3832,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3860,7 +3858,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3870,13 +3868,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555621</v>
+        <v>555481</v>
       </c>
       <c r="R32" t="n">
-        <v>6955246</v>
+        <v>6955375</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3905,7 +3903,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3915,7 +3913,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3942,7 +3940,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124765997</v>
+        <v>124766516</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3976,24 +3974,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555481</v>
+        <v>555312</v>
       </c>
       <c r="R33" t="n">
-        <v>6955375</v>
+        <v>6955333</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4025,7 +4020,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4035,7 +4030,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,7 +4062,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124766526</v>
+        <v>124766529</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555434</v>
+        <v>555486</v>
       </c>
       <c r="R34" t="n">
-        <v>6955374</v>
+        <v>6955384</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4183,7 +4183,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766529</v>
+        <v>124766526</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555486</v>
+        <v>555434</v>
       </c>
       <c r="R35" t="n">
-        <v>6955384</v>
+        <v>6955374</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124765999</v>
+        <v>124766514</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3600,20 +3600,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3622,27 +3622,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555621</v>
+        <v>555385</v>
       </c>
       <c r="R30" t="n">
-        <v>6955246</v>
+        <v>6955319</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3669,19 +3666,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>06:00</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3708,10 +3700,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124766514</v>
+        <v>124766516</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3724,16 +3716,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3753,10 +3745,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555385</v>
+        <v>555312</v>
       </c>
       <c r="R31" t="n">
-        <v>6955319</v>
+        <v>6955333</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3786,14 +3778,24 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>barkfläk färsk tall</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3940,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124766516</v>
+        <v>124765999</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3952,20 +3954,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3974,24 +3976,27 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555312</v>
+        <v>555621</v>
       </c>
       <c r="R33" t="n">
-        <v>6955333</v>
+        <v>6955246</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4020,7 +4025,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4030,12 +4035,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,7 +4062,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124766529</v>
+        <v>124766526</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555486</v>
+        <v>555434</v>
       </c>
       <c r="R34" t="n">
-        <v>6955384</v>
+        <v>6955374</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4183,7 +4183,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766526</v>
+        <v>124766527</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555434</v>
+        <v>555322</v>
       </c>
       <c r="R35" t="n">
-        <v>6955374</v>
+        <v>6955344</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766527</v>
+        <v>124766529</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555322</v>
+        <v>555486</v>
       </c>
       <c r="R36" t="n">
-        <v>6955344</v>
+        <v>6955384</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124766514</v>
+        <v>124765997</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3604,16 +3604,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3622,21 +3622,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555385</v>
+        <v>555481</v>
       </c>
       <c r="R30" t="n">
-        <v>6955319</v>
+        <v>6955375</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3666,14 +3669,19 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>barkfläk färsk tall</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3822,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124765997</v>
+        <v>124765999</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3834,20 +3842,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3860,7 +3868,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3870,13 +3878,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555481</v>
+        <v>555621</v>
       </c>
       <c r="R32" t="n">
-        <v>6955375</v>
+        <v>6955246</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3905,7 +3913,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3915,7 +3923,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3942,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124765999</v>
+        <v>124766514</v>
       </c>
       <c r="B33" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3954,20 +3962,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3976,27 +3984,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555621</v>
+        <v>555385</v>
       </c>
       <c r="R33" t="n">
-        <v>6955246</v>
+        <v>6955319</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4023,19 +4028,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>06:00</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4183,7 +4183,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766527</v>
+        <v>124766529</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555322</v>
+        <v>555486</v>
       </c>
       <c r="R35" t="n">
-        <v>6955344</v>
+        <v>6955384</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766529</v>
+        <v>124766527</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555486</v>
+        <v>555322</v>
       </c>
       <c r="R36" t="n">
-        <v>6955384</v>
+        <v>6955344</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124765997</v>
+        <v>124766514</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3604,16 +3604,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3622,24 +3622,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555481</v>
+        <v>555385</v>
       </c>
       <c r="R30" t="n">
-        <v>6955375</v>
+        <v>6955319</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3669,19 +3666,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>06:10</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3830,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124765999</v>
+        <v>124765997</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3842,20 +3834,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3868,7 +3860,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3878,13 +3870,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555621</v>
+        <v>555481</v>
       </c>
       <c r="R32" t="n">
-        <v>6955246</v>
+        <v>6955375</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3913,7 +3905,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3923,7 +3915,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3950,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124766514</v>
+        <v>124765999</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3962,20 +3954,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3984,24 +3976,27 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555385</v>
+        <v>555621</v>
       </c>
       <c r="R33" t="n">
-        <v>6955319</v>
+        <v>6955246</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4028,14 +4023,19 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>barkfläk färsk tall</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,7 +4062,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124766526</v>
+        <v>124766527</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555434</v>
+        <v>555322</v>
       </c>
       <c r="R34" t="n">
-        <v>6955374</v>
+        <v>6955344</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766527</v>
+        <v>124766526</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555322</v>
+        <v>555434</v>
       </c>
       <c r="R36" t="n">
-        <v>6955344</v>
+        <v>6955374</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124765997</v>
+        <v>124765999</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3860,7 +3860,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555481</v>
+        <v>555621</v>
       </c>
       <c r="R32" t="n">
-        <v>6955375</v>
+        <v>6955246</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3942,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124765999</v>
+        <v>124765997</v>
       </c>
       <c r="B33" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3954,20 +3954,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3980,7 +3980,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555621</v>
+        <v>555481</v>
       </c>
       <c r="R33" t="n">
-        <v>6955246</v>
+        <v>6955375</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124766514</v>
+        <v>124766516</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3604,16 +3604,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555385</v>
+        <v>555312</v>
       </c>
       <c r="R30" t="n">
-        <v>6955319</v>
+        <v>6955333</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3666,14 +3666,24 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>barkfläk färsk tall</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3700,10 +3710,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124766516</v>
+        <v>124765999</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3712,20 +3722,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3734,24 +3744,27 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555312</v>
+        <v>555621</v>
       </c>
       <c r="R31" t="n">
-        <v>6955333</v>
+        <v>6955246</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3780,7 +3793,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3790,12 +3803,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3822,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124765999</v>
+        <v>124765997</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3834,20 +3842,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3860,7 +3868,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3870,13 +3878,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555621</v>
+        <v>555481</v>
       </c>
       <c r="R32" t="n">
-        <v>6955246</v>
+        <v>6955375</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3905,7 +3913,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3915,7 +3923,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3942,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124765997</v>
+        <v>124766514</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3958,16 +3966,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3976,24 +3984,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555481</v>
+        <v>555385</v>
       </c>
       <c r="R33" t="n">
-        <v>6955375</v>
+        <v>6955319</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4023,19 +4028,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>06:10</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4183,7 +4183,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766529</v>
+        <v>124766526</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555486</v>
+        <v>555434</v>
       </c>
       <c r="R35" t="n">
-        <v>6955384</v>
+        <v>6955374</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766526</v>
+        <v>124766529</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555434</v>
+        <v>555486</v>
       </c>
       <c r="R36" t="n">
-        <v>6955374</v>
+        <v>6955384</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124766516</v>
+        <v>124766514</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>57632</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3604,16 +3604,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555312</v>
+        <v>555385</v>
       </c>
       <c r="R30" t="n">
-        <v>6955333</v>
+        <v>6955319</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3666,24 +3666,14 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>08:29</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>08:29</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska barkfläk</t>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3713,7 +3703,7 @@
         <v>124765999</v>
       </c>
       <c r="B31" t="n">
-        <v>57883</v>
+        <v>58001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3833,7 +3823,7 @@
         <v>124765997</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3950,10 +3940,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124766514</v>
+        <v>124766516</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3966,16 +3956,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3995,10 +3985,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555385</v>
+        <v>555312</v>
       </c>
       <c r="R33" t="n">
-        <v>6955319</v>
+        <v>6955333</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4028,14 +4018,24 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>barkfläk färsk tall</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4065,7 +4065,7 @@
         <v>124766527</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>124766526</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>124766529</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3700,10 +3700,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124765999</v>
+        <v>124765997</v>
       </c>
       <c r="B31" t="n">
-        <v>58001</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3712,20 +3712,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3738,7 +3738,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3748,13 +3748,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555621</v>
+        <v>555481</v>
       </c>
       <c r="R31" t="n">
-        <v>6955246</v>
+        <v>6955375</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3820,10 +3820,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124765997</v>
+        <v>124765999</v>
       </c>
       <c r="B32" t="n">
-        <v>57635</v>
+        <v>58001</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3832,20 +3832,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3858,7 +3858,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3868,13 +3868,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555481</v>
+        <v>555621</v>
       </c>
       <c r="R32" t="n">
-        <v>6955375</v>
+        <v>6955246</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4062,7 +4062,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124766527</v>
+        <v>124766529</v>
       </c>
       <c r="B34" t="n">
         <v>57635</v>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555322</v>
+        <v>555486</v>
       </c>
       <c r="R34" t="n">
-        <v>6955344</v>
+        <v>6955384</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4183,7 +4183,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766526</v>
+        <v>124766527</v>
       </c>
       <c r="B35" t="n">
         <v>57635</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555434</v>
+        <v>555322</v>
       </c>
       <c r="R35" t="n">
-        <v>6955374</v>
+        <v>6955344</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766529</v>
+        <v>124766526</v>
       </c>
       <c r="B36" t="n">
         <v>57635</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555486</v>
+        <v>555434</v>
       </c>
       <c r="R36" t="n">
-        <v>6955384</v>
+        <v>6955374</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -3820,10 +3820,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124765999</v>
+        <v>124766516</v>
       </c>
       <c r="B32" t="n">
-        <v>58001</v>
+        <v>57635</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3832,20 +3832,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3854,27 +3854,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555621</v>
+        <v>555312</v>
       </c>
       <c r="R32" t="n">
-        <v>6955246</v>
+        <v>6955333</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3903,7 +3900,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3913,7 +3910,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3940,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124766516</v>
+        <v>124765999</v>
       </c>
       <c r="B33" t="n">
-        <v>57635</v>
+        <v>58001</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3952,20 +3954,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3974,24 +3976,27 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555312</v>
+        <v>555621</v>
       </c>
       <c r="R33" t="n">
-        <v>6955333</v>
+        <v>6955246</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4020,7 +4025,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4030,12 +4035,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -4067,11 +4067,6 @@
       <c r="B34" t="n">
         <v>57635</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4183,16 +4178,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766527</v>
+        <v>124766526</v>
       </c>
       <c r="B35" t="n">
         <v>57635</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4232,10 +4222,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555322</v>
+        <v>555434</v>
       </c>
       <c r="R35" t="n">
-        <v>6955344</v>
+        <v>6955374</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4304,16 +4294,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766526</v>
+        <v>124766527</v>
       </c>
       <c r="B36" t="n">
         <v>57635</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4353,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555434</v>
+        <v>555322</v>
       </c>
       <c r="R36" t="n">
-        <v>6955374</v>
+        <v>6955344</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -4413,7 +4413,7 @@
         <v>126737238</v>
       </c>
       <c r="B37" t="n">
-        <v>91947</v>
+        <v>92021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>126737900</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126737734</v>
+        <v>126737275</v>
       </c>
       <c r="B39" t="n">
-        <v>91245</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4625,21 +4625,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555394</v>
+        <v>555530</v>
       </c>
       <c r="R39" t="n">
-        <v>6955371</v>
+        <v>6955377</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126737275</v>
+        <v>126737734</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555530</v>
+        <v>555394</v>
       </c>
       <c r="R40" t="n">
-        <v>6955377</v>
+        <v>6955371</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,7 +4821,7 @@
         <v>126739095</v>
       </c>
       <c r="B41" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -4413,7 +4413,7 @@
         <v>126737238</v>
       </c>
       <c r="B37" t="n">
-        <v>92021</v>
+        <v>92027</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>126737900</v>
       </c>
       <c r="B38" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126737275</v>
+        <v>126737734</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>91325</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4625,21 +4625,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555530</v>
+        <v>555394</v>
       </c>
       <c r="R39" t="n">
-        <v>6955377</v>
+        <v>6955371</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126737734</v>
+        <v>126737275</v>
       </c>
       <c r="B40" t="n">
-        <v>91319</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555394</v>
+        <v>555530</v>
       </c>
       <c r="R40" t="n">
-        <v>6955371</v>
+        <v>6955377</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,7 +4821,7 @@
         <v>126739095</v>
       </c>
       <c r="B41" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -4614,10 +4614,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126737734</v>
+        <v>126737275</v>
       </c>
       <c r="B39" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4625,21 +4625,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555394</v>
+        <v>555530</v>
       </c>
       <c r="R39" t="n">
-        <v>6955371</v>
+        <v>6955377</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126737275</v>
+        <v>126737734</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555530</v>
+        <v>555394</v>
       </c>
       <c r="R40" t="n">
-        <v>6955377</v>
+        <v>6955371</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -4413,7 +4413,7 @@
         <v>126737238</v>
       </c>
       <c r="B37" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>126737900</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126737275</v>
+        <v>126737734</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4625,21 +4625,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555530</v>
+        <v>555394</v>
       </c>
       <c r="R39" t="n">
-        <v>6955377</v>
+        <v>6955371</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126737734</v>
+        <v>126737275</v>
       </c>
       <c r="B40" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555394</v>
+        <v>555530</v>
       </c>
       <c r="R40" t="n">
-        <v>6955371</v>
+        <v>6955377</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,7 +4821,7 @@
         <v>126739095</v>
       </c>
       <c r="B41" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -4413,7 +4413,7 @@
         <v>126737238</v>
       </c>
       <c r="B37" t="n">
-        <v>92028</v>
+        <v>92032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>126737900</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126737734</v>
+        <v>126737275</v>
       </c>
       <c r="B39" t="n">
-        <v>91326</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4625,21 +4625,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555394</v>
+        <v>555530</v>
       </c>
       <c r="R39" t="n">
-        <v>6955371</v>
+        <v>6955377</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126737275</v>
+        <v>126737734</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>91330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555530</v>
+        <v>555394</v>
       </c>
       <c r="R40" t="n">
-        <v>6955377</v>
+        <v>6955371</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,7 +4821,7 @@
         <v>126739095</v>
       </c>
       <c r="B41" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -4413,7 +4413,7 @@
         <v>126737238</v>
       </c>
       <c r="B37" t="n">
-        <v>92032</v>
+        <v>92021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>126737900</v>
       </c>
       <c r="B38" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>126737275</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>126737734</v>
       </c>
       <c r="B40" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>126739095</v>
       </c>
       <c r="B41" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -4413,7 +4413,7 @@
         <v>126737238</v>
       </c>
       <c r="B37" t="n">
-        <v>92021</v>
+        <v>92032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>126737900</v>
       </c>
       <c r="B38" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>126737275</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>126737734</v>
       </c>
       <c r="B40" t="n">
-        <v>91319</v>
+        <v>91330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>126739095</v>
       </c>
       <c r="B41" t="n">
-        <v>91319</v>
+        <v>91330</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113177827</v>
+        <v>126737238</v>
       </c>
       <c r="B2" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555388</v>
+        <v>555529</v>
       </c>
       <c r="R2" t="n">
-        <v>6955406</v>
+        <v>6955376</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,45 +759,28 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>skiktad naturskogsartad barrskog i nordsida</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # klen trädformig rönn</t>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119532134</v>
+        <v>126737734</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555449</v>
+        <v>555394</v>
       </c>
       <c r="R3" t="n">
-        <v>6955393</v>
+        <v>6955371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,17 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,31 +858,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119532189</v>
+        <v>126739095</v>
       </c>
       <c r="B4" t="n">
-        <v>91825</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1968</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555432</v>
+        <v>555154</v>
       </c>
       <c r="R4" t="n">
-        <v>6955262</v>
+        <v>6955291</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,53 +960,53 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119532182</v>
+        <v>119532189</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555396</v>
+        <v>555432</v>
       </c>
       <c r="R5" t="n">
-        <v>6955386</v>
+        <v>6955262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,19 +1078,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119532209</v>
+        <v>119532206</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1145,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555183</v>
+        <v>555084</v>
       </c>
       <c r="R6" t="n">
-        <v>6955343</v>
+        <v>6955311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,37 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119532146</v>
+        <v>119532209</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1247,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555445</v>
+        <v>555183</v>
       </c>
       <c r="R7" t="n">
-        <v>6955336</v>
+        <v>6955343</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,12 +1240,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,37 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119532152</v>
+        <v>119532211</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555363</v>
+        <v>555292</v>
       </c>
       <c r="R8" t="n">
-        <v>6955341</v>
+        <v>6955404</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,12 +1337,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,37 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119532171</v>
+        <v>119532143</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555162</v>
+        <v>555222</v>
       </c>
       <c r="R9" t="n">
-        <v>6955287</v>
+        <v>6955368</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,37 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119532150</v>
+        <v>119532214</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555381</v>
+        <v>555215</v>
       </c>
       <c r="R10" t="n">
-        <v>6955359</v>
+        <v>6955365</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,12 +1531,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,15 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119532200</v>
+        <v>119532120</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555451</v>
+        <v>555364</v>
       </c>
       <c r="R11" t="n">
-        <v>6955405</v>
+        <v>6955302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,12 +1628,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1717,54 +1660,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119532142</v>
+        <v>119532198</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555408</v>
+        <v>555391</v>
       </c>
       <c r="R12" t="n">
-        <v>6955266</v>
+        <v>6955385</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,17 +1725,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>hörd</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,37 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119532120</v>
+        <v>119532200</v>
       </c>
       <c r="B13" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1868,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555364</v>
+        <v>555451</v>
       </c>
       <c r="R13" t="n">
-        <v>6955302</v>
+        <v>6955405</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,12 +1822,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,15 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119532175</v>
+        <v>119532202</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555175</v>
+        <v>555532</v>
       </c>
       <c r="R14" t="n">
-        <v>6955324</v>
+        <v>6955432</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2032,50 +1951,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119532206</v>
+        <v>126737275</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555084</v>
+        <v>555530</v>
       </c>
       <c r="R15" t="n">
-        <v>6955311</v>
+        <v>6955377</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,12 +2016,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,53 +2032,53 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119532141</v>
+        <v>113177827</v>
       </c>
       <c r="B16" t="n">
-        <v>91843</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003297</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2174,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555221</v>
+        <v>555388</v>
       </c>
       <c r="R16" t="n">
-        <v>6955359</v>
+        <v>6955406</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,12 +2118,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2218,69 +2132,84 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>skiktad naturskogsartad barrskog i nordsida</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>1 substratenheter # klen trädformig rönn</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119532202</v>
+        <v>119532142</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555532</v>
+        <v>555408</v>
       </c>
       <c r="R17" t="n">
-        <v>6955432</v>
+        <v>6955266</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,12 +2236,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hörd</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,53 +2273,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119532177</v>
+        <v>124766514</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555268</v>
+        <v>555385</v>
       </c>
       <c r="R18" t="n">
-        <v>6955365</v>
+        <v>6955319</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2409,12 +2343,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>barkfläk färsk tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,49 +2368,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119532140</v>
+        <v>119532133</v>
       </c>
       <c r="B19" t="n">
-        <v>100080</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2481,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555631</v>
+        <v>555107</v>
       </c>
       <c r="R19" t="n">
-        <v>6955317</v>
+        <v>6955310</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2517,6 +2451,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,37 +2482,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119532179</v>
+        <v>119532134</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2583,10 +2517,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555273</v>
+        <v>555449</v>
       </c>
       <c r="R20" t="n">
-        <v>6955369</v>
+        <v>6955393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2619,6 +2553,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2645,15 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119532198</v>
+        <v>119532135</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2661,34 +2595,54 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555391</v>
+        <v>555578</v>
       </c>
       <c r="R21" t="n">
-        <v>6955385</v>
+        <v>6955449</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2747,53 +2701,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119532211</v>
+        <v>124765997</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555292</v>
+        <v>555481</v>
       </c>
       <c r="R22" t="n">
-        <v>6955404</v>
+        <v>6955375</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2817,12 +2774,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,27 +2804,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119532187</v>
+        <v>124766516</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2865,37 +2827,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555182</v>
+        <v>555312</v>
       </c>
       <c r="R23" t="n">
-        <v>6955285</v>
+        <v>6955333</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2919,12 +2886,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2939,27 +2921,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119532135</v>
+        <v>124766526</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2989,20 +2966,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3011,13 +2977,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555578</v>
+        <v>555434</v>
       </c>
       <c r="R24" t="n">
-        <v>6955449</v>
+        <v>6955374</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3041,12 +3007,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,65 +3037,69 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119532143</v>
+        <v>124766527</v>
       </c>
       <c r="B25" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555222</v>
+        <v>555322</v>
       </c>
       <c r="R25" t="n">
-        <v>6955368</v>
+        <v>6955344</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3143,12 +3123,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,65 +3153,69 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119532173</v>
+        <v>124766529</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555080</v>
+        <v>555486</v>
       </c>
       <c r="R26" t="n">
-        <v>6955298</v>
+        <v>6955384</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3245,12 +3239,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3265,44 +3269,39 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119532133</v>
+        <v>124765999</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3311,19 +3310,27 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555107</v>
+        <v>555621</v>
       </c>
       <c r="R27" t="n">
-        <v>6955310</v>
+        <v>6955246</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3347,17 +3354,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,49 +3384,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119532214</v>
+        <v>119532146</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3424,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555215</v>
+        <v>555445</v>
       </c>
       <c r="R28" t="n">
-        <v>6955365</v>
+        <v>6955336</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,12 +3461,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3489,12 +3496,7 @@
         <v>119532148</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3588,58 +3590,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124766514</v>
+        <v>119532150</v>
       </c>
       <c r="B30" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555385</v>
+        <v>555381</v>
       </c>
       <c r="R30" t="n">
-        <v>6955319</v>
+        <v>6955359</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3663,17 +3655,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>barkfläk färsk tall</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3688,73 +3675,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124765997</v>
+        <v>119532152</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555481</v>
+        <v>555363</v>
       </c>
       <c r="R31" t="n">
-        <v>6955375</v>
+        <v>6955341</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3778,22 +3752,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>06:10</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>06:10</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3808,70 +3772,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124766516</v>
+        <v>119532171</v>
       </c>
       <c r="B32" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555312</v>
+        <v>555162</v>
       </c>
       <c r="R32" t="n">
-        <v>6955333</v>
+        <v>6955287</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3895,27 +3849,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>08:29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3930,73 +3869,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124765999</v>
+        <v>119532173</v>
       </c>
       <c r="B33" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555621</v>
+        <v>555080</v>
       </c>
       <c r="R33" t="n">
-        <v>6955246</v>
+        <v>6955298</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4020,22 +3946,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4050,69 +3966,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124766529</v>
+        <v>119532175</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555486</v>
+        <v>555175</v>
       </c>
       <c r="R34" t="n">
-        <v>6955384</v>
+        <v>6955324</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4136,22 +4043,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>06:38</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>06:38</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,69 +4063,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124766526</v>
+        <v>119532177</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555434</v>
+        <v>555268</v>
       </c>
       <c r="R35" t="n">
-        <v>6955374</v>
+        <v>6955365</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4252,22 +4140,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>06:40</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>06:40</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,69 +4160,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124766527</v>
+        <v>119532179</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555322</v>
+        <v>555273</v>
       </c>
       <c r="R36" t="n">
-        <v>6955344</v>
+        <v>6955369</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4368,22 +4237,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>06:40</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>06:40</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4398,22 +4257,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126737238</v>
+        <v>119532182</v>
       </c>
       <c r="B37" t="n">
-        <v>92032</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4421,34 +4280,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555529</v>
+        <v>555396</v>
       </c>
       <c r="R37" t="n">
-        <v>6955376</v>
+        <v>6955386</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,12 +4334,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,21 +4350,16 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4515,7 +4369,7 @@
         <v>126737900</v>
       </c>
       <c r="B38" t="n">
-        <v>98447</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,45 +4468,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126737275</v>
+        <v>119532140</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>101228</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>222771</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555530</v>
+        <v>555631</v>
       </c>
       <c r="R39" t="n">
-        <v>6955377</v>
+        <v>6955317</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4679,12 +4533,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4695,66 +4549,61 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126737734</v>
+        <v>119532141</v>
       </c>
       <c r="B40" t="n">
-        <v>91330</v>
+        <v>93200</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6003297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spricktaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum glaucopus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555394</v>
+        <v>555221</v>
       </c>
       <c r="R40" t="n">
-        <v>6955371</v>
+        <v>6955359</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4781,12 +4630,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,128 +4644,22 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>126739095</v>
-      </c>
-      <c r="B41" t="n">
-        <v>91330</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>555154</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6955291</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31470-2024 artfynd.xlsx
+++ b/artfynd/A 31470-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126737238</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126737734</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126739095</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532189</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532206</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532209</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532211</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532143</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532214</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532120</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532198</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532200</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532202</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126737275</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113177827</t>
         </is>
       </c>
     </row>
@@ -2270,6 +2350,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532142</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2377,6 +2462,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124766514</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2479,6 +2569,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532133</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2581,6 +2676,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532134</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2698,6 +2798,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532135</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2813,6 +2918,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124765997</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2930,6 +3040,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124766516</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3046,6 +3161,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124766526</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3162,6 +3282,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124766527</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3278,6 +3403,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124766529</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3393,6 +3523,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124765999</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3490,6 +3625,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532146</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3587,6 +3727,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532148</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3684,6 +3829,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532150</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3781,6 +3931,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532152</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3878,6 +4033,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532171</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3975,6 +4135,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532173</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4072,6 +4237,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532175</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4169,6 +4339,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532177</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4266,6 +4441,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532179</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4363,6 +4543,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532182</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4465,6 +4650,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126737900</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4562,6 +4752,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532140</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4660,8 +4855,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532141</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>